--- a/data/trans_dic/P19C01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C01-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,88; 34,46</t>
+          <t>22,09; 34,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,98; 23,7</t>
+          <t>14,04; 23,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,84; 30,56</t>
+          <t>18,55; 30,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91,22; 96,33</t>
+          <t>91,25; 96,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,55; 43,52</t>
+          <t>29,85; 43,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,4; 23,08</t>
+          <t>12,88; 23,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,9; 37,72</t>
+          <t>25,77; 37,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>92,88; 96,59</t>
+          <t>92,87; 96,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,65; 37,23</t>
+          <t>27,25; 37,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,86; 21,93</t>
+          <t>14,68; 22,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,89; 32,3</t>
+          <t>24,21; 32,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,86; 95,95</t>
+          <t>92,86; 96,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,25; 34,93</t>
+          <t>24,8; 34,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,69; 34,1</t>
+          <t>24,2; 34,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,36; 31,6</t>
+          <t>22,55; 32,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,79; 45,85</t>
+          <t>34,85; 45,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,69; 34,2</t>
+          <t>25,22; 33,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,25; 33,88</t>
+          <t>24,66; 33,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,92; 39,59</t>
+          <t>29,94; 39,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,86; 45,72</t>
+          <t>38,03; 45,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,75; 33,04</t>
+          <t>26,49; 32,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,25; 32,7</t>
+          <t>25,98; 32,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,49; 34,28</t>
+          <t>27,53; 34,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,28; 44,42</t>
+          <t>37,64; 44,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,15; 30,03</t>
+          <t>18,54; 29,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,08; 38,93</t>
+          <t>28,01; 39,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,28; 43,31</t>
+          <t>31,5; 43,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,11; 48,01</t>
+          <t>36,41; 47,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,62; 30,97</t>
+          <t>19,91; 30,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,02; 41,39</t>
+          <t>30,83; 41,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,07; 45,09</t>
+          <t>34,11; 45,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,35; 47,04</t>
+          <t>37,16; 46,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,24; 28,9</t>
+          <t>20,94; 28,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,2; 38,74</t>
+          <t>31,25; 39,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,58; 42,75</t>
+          <t>34,6; 42,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,02; 46,02</t>
+          <t>38,32; 45,56</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,77; 42,39</t>
+          <t>31,41; 42,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,25; 35,62</t>
+          <t>24,24; 35,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,54; 35,97</t>
+          <t>25,42; 35,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,11; 39,42</t>
+          <t>25,84; 39,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,17; 40,57</t>
+          <t>30,01; 40,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,73; 41,63</t>
+          <t>30,94; 41,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,27; 31,83</t>
+          <t>22,01; 31,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,61; 64,55</t>
+          <t>27,15; 64,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,97; 39,83</t>
+          <t>31,75; 39,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,27; 36,82</t>
+          <t>29,45; 37,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,21; 32,26</t>
+          <t>25,27; 32,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,74; 53,93</t>
+          <t>28,99; 52,73</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,82; 47,81</t>
+          <t>32,39; 47,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,37; 47,47</t>
+          <t>32,38; 46,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,98; 72,57</t>
+          <t>55,48; 73,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,92; 92,22</t>
+          <t>85,72; 92,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,61; 50,8</t>
+          <t>35,63; 50,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,29; 53,49</t>
+          <t>39,16; 53,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,06; 75,91</t>
+          <t>60,11; 74,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87,03; 92,69</t>
+          <t>86,94; 92,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36,24; 46,64</t>
+          <t>36,39; 47,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37,7; 48,4</t>
+          <t>37,38; 47,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60,34; 71,94</t>
+          <t>60,55; 71,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,53; 91,93</t>
+          <t>87,72; 91,85</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,08; 31,74</t>
+          <t>18,36; 30,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,74; 36,64</t>
+          <t>24,82; 36,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,01; 46,0</t>
+          <t>33,02; 46,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36,43; 48,85</t>
+          <t>36,69; 48,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,68; 38,54</t>
+          <t>25,23; 38,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,27; 44,85</t>
+          <t>34,06; 45,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,66; 50,98</t>
+          <t>38,91; 51,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46,61; 56,37</t>
+          <t>46,64; 56,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,59; 32,57</t>
+          <t>23,96; 32,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,63; 39,28</t>
+          <t>30,51; 39,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38,24; 47,3</t>
+          <t>37,88; 47,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,2; 51,01</t>
+          <t>42,89; 50,93</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,1; 25,89</t>
+          <t>18,02; 26,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,65; 35,11</t>
+          <t>26,55; 34,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45,14; 54,87</t>
+          <t>44,36; 54,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54,9; 63,7</t>
+          <t>54,99; 63,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,28; 29,7</t>
+          <t>22,22; 29,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,53; 43,53</t>
+          <t>35,74; 43,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,85; 54,03</t>
+          <t>44,38; 53,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,78; 58,57</t>
+          <t>19,83; 58,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,59; 27,02</t>
+          <t>21,4; 26,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32,21; 38,13</t>
+          <t>32,51; 38,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46,35; 53,09</t>
+          <t>45,91; 52,89</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,08; 59,41</t>
+          <t>31,35; 59,32</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31,4; 39,65</t>
+          <t>30,98; 39,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,34; 30,89</t>
+          <t>23,78; 30,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,34; 55,68</t>
+          <t>47,11; 55,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,55; 69,43</t>
+          <t>23,32; 69,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,86; 37,68</t>
+          <t>29,3; 37,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,11; 35,78</t>
+          <t>28,22; 35,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,59; 56,62</t>
+          <t>49,49; 57,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>70,56; 76,4</t>
+          <t>70,87; 76,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,75; 37,16</t>
+          <t>31,66; 37,24</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,96; 32,24</t>
+          <t>27,29; 32,36</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49,75; 55,13</t>
+          <t>49,51; 54,99</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,11; 71,86</t>
+          <t>37,6; 71,78</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,17; 31,6</t>
+          <t>27,99; 31,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27,58; 31,25</t>
+          <t>27,78; 31,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38,95; 42,93</t>
+          <t>38,77; 42,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41,03; 58,15</t>
+          <t>41,74; 58,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,68; 33,38</t>
+          <t>29,71; 33,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,54; 36,01</t>
+          <t>32,55; 35,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,56; 45,32</t>
+          <t>41,61; 45,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>44,31; 60,07</t>
+          <t>44,37; 60,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,41; 31,95</t>
+          <t>29,36; 31,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,56; 33,11</t>
+          <t>30,74; 33,29</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40,75; 43,45</t>
+          <t>40,83; 43,41</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>47,86; 58,51</t>
+          <t>48,01; 57,99</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo</t>
+          <t>Población cuyo motivo por su última visita al dentista fue una revisión o chequeo (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41890; 65988</t>
+          <t>42296; 66136</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35030; 59387</t>
+          <t>35170; 58809</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46203; 74928</t>
+          <t>45488; 74280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>278623; 294217</t>
+          <t>278707; 294157</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59463; 87576</t>
+          <t>60069; 87934</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33526; 57768</t>
+          <t>32245; 57597</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63801; 92923</t>
+          <t>63487; 93399</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>267126; 277809</t>
+          <t>267090; 277731</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>108604; 146220</t>
+          <t>107009; 145568</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74432; 109855</t>
+          <t>73508; 110202</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117415; 158753</t>
+          <t>119003; 159417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>550670; 569038</t>
+          <t>550679; 569640</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>103480; 143124</t>
+          <t>101624; 142154</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>100321; 138562</t>
+          <t>98348; 138740</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81213; 114777</t>
+          <t>81879; 116888</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>176365; 232431</t>
+          <t>176671; 231550</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>113359; 150898</t>
+          <t>111261; 149439</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>110292; 147982</t>
+          <t>107739; 148385</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>117682; 155709</t>
+          <t>117754; 153776</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>189889; 229283</t>
+          <t>190762; 229127</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>227642; 281185</t>
+          <t>225379; 280499</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>221350; 275703</t>
+          <t>219018; 276166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>207969; 259316</t>
+          <t>208262; 260528</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>376020; 447956</t>
+          <t>379633; 447956</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45298; 71030</t>
+          <t>43862; 70074</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82450; 114329</t>
+          <t>82267; 114987</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93767; 125813</t>
+          <t>91517; 125703</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>108753; 144611</t>
+          <t>109675; 144135</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>59545; 89454</t>
+          <t>57490; 86888</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>101662; 135611</t>
+          <t>101012; 136480</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>104865; 138766</t>
+          <t>104974; 138623</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>125222; 157708</t>
+          <t>124592; 155986</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>111596; 151822</t>
+          <t>109988; 149800</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>193877; 240737</t>
+          <t>194183; 243076</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>206858; 255776</t>
+          <t>206982; 254409</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>241959; 292932</t>
+          <t>243906; 289965</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82313; 113405</t>
+          <t>84025; 114298</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75926; 111531</t>
+          <t>75898; 110944</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84281; 118713</t>
+          <t>83895; 118409</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80985; 122251</t>
+          <t>80120; 121726</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>90363; 121510</t>
+          <t>89899; 121124</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>105332; 142707</t>
+          <t>106070; 143120</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77691; 111052</t>
+          <t>76785; 110295</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>130721; 305632</t>
+          <t>128536; 303113</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181301; 225864</t>
+          <t>180023; 225134</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191965; 241484</t>
+          <t>193173; 244221</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>171182; 218984</t>
+          <t>171559; 222256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>233048; 422556</t>
+          <t>227198; 413150</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55882; 81415</t>
+          <t>55159; 80614</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>62160; 91166</t>
+          <t>62194; 89491</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65552; 86521</t>
+          <t>66141; 87230</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>143028; 155322</t>
+          <t>144377; 155729</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>61929; 88337</t>
+          <t>61966; 87886</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76447; 104083</t>
+          <t>76191; 104854</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88841; 110452</t>
+          <t>87458; 108976</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>176052; 187497</t>
+          <t>175873; 187627</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>124721; 160520</t>
+          <t>125243; 162369</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145764; 187131</t>
+          <t>144520; 184673</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159730; 190451</t>
+          <t>160292; 189410</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>324482; 340810</t>
+          <t>325182; 340521</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36110; 60079</t>
+          <t>34751; 58350</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>61844; 91587</t>
+          <t>62054; 91072</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77124; 107473</t>
+          <t>77146; 107594</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92438; 123945</t>
+          <t>93106; 122900</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52522; 78820</t>
+          <t>51597; 78292</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>88117; 118769</t>
+          <t>90193; 120666</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95549; 125989</t>
+          <t>96153; 127726</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>114814; 138877</t>
+          <t>114897; 139839</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92871; 128242</t>
+          <t>94325; 129831</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>157683; 202217</t>
+          <t>157082; 200900</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>183840; 227384</t>
+          <t>182122; 226136</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>216040; 255084</t>
+          <t>214474; 254698</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>84035; 120199</t>
+          <t>83657; 120976</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>153254; 201889</t>
+          <t>152661; 197784</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>199673; 242673</t>
+          <t>196207; 241334</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>329615; 382437</t>
+          <t>330173; 382762</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>120160; 160218</t>
+          <t>119821; 161677</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>222429; 272467</t>
+          <t>223740; 272845</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>218466; 263143</t>
+          <t>216147; 262027</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>172156; 485145</t>
+          <t>164268; 485631</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>216665; 271193</t>
+          <t>214821; 270757</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>386875; 457977</t>
+          <t>390473; 457595</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>430749; 493380</t>
+          <t>426626; 491546</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>444028; 848841</t>
+          <t>447863; 847552</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>165489; 208955</t>
+          <t>163257; 206130</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>147936; 195826</t>
+          <t>150738; 196151</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>303076; 356477</t>
+          <t>301620; 354148</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>195825; 630886</t>
+          <t>211923; 630934</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>176635; 222892</t>
+          <t>173330; 220979</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>197407; 251263</t>
+          <t>198211; 247460</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>335898; 391462</t>
+          <t>342165; 395464</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>496698; 537773</t>
+          <t>498874; 540764</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>355159; 415631</t>
+          <t>354139; 416589</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>360233; 430834</t>
+          <t>364669; 432449</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>662516; 734108</t>
+          <t>659270; 732212</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>550046; 1158807</t>
+          <t>606284; 1157496</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>692031; 776288</t>
+          <t>687407; 777003</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>803968; 910699</t>
+          <t>809706; 913371</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1037677; 1143813</t>
+          <t>1032978; 1137089</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1376402; 1951046</t>
+          <t>1400399; 1951534</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>813224; 914498</t>
+          <t>813931; 907265</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1023560; 1132517</t>
+          <t>1023692; 1131777</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1191683; 1299392</t>
+          <t>1193046; 1302499</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1585742; 2149709</t>
+          <t>1587861; 2147506</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1528215; 1660205</t>
+          <t>1525596; 1658507</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1851991; 2006171</t>
+          <t>1863103; 2017148</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2254138; 2403527</t>
+          <t>2258370; 2401253</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3318150; 4056925</t>
+          <t>3328718; 4020537</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C01-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,09; 34,54</t>
+          <t>21,9; 34,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,04; 23,47</t>
+          <t>14,48; 23,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,55; 30,29</t>
+          <t>19,12; 30,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91,25; 96,31</t>
+          <t>88,57; 94,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,85; 43,7</t>
+          <t>29,56; 43,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 23,01</t>
+          <t>13,06; 22,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,77; 37,92</t>
+          <t>25,57; 37,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>92,87; 96,57</t>
+          <t>92,9; 96,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,25; 37,07</t>
+          <t>27,54; 37,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,68; 22,0</t>
+          <t>14,85; 22,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,21; 32,43</t>
+          <t>23,95; 32,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,86; 96,05</t>
+          <t>91,69; 95,22</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,55%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,8; 34,69</t>
+          <t>25,25; 34,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,2; 34,14</t>
+          <t>25,18; 34,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,55; 32,19</t>
+          <t>22,69; 32,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34,85; 45,67</t>
+          <t>35,92; 46,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,22; 33,87</t>
+          <t>25,02; 34,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,66; 33,97</t>
+          <t>25,02; 33,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,94; 39,1</t>
+          <t>29,67; 39,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,03; 45,68</t>
+          <t>38,58; 46,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,49; 32,96</t>
+          <t>26,68; 32,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,98; 32,75</t>
+          <t>26,01; 32,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,53; 34,44</t>
+          <t>27,45; 34,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,64; 44,42</t>
+          <t>38,04; 44,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,54; 29,63</t>
+          <t>18,34; 29,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,01; 39,16</t>
+          <t>28,84; 39,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,5; 43,27</t>
+          <t>32,71; 43,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36,41; 47,85</t>
+          <t>35,96; 46,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,91; 30,09</t>
+          <t>20,95; 30,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,83; 41,65</t>
+          <t>31,21; 42,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,11; 45,04</t>
+          <t>34,13; 44,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,16; 46,52</t>
+          <t>37,24; 46,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,94; 28,51</t>
+          <t>20,76; 28,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,25; 39,12</t>
+          <t>30,96; 38,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34,6; 42,52</t>
+          <t>34,18; 42,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,32; 45,56</t>
+          <t>37,97; 45,38</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,41; 42,72</t>
+          <t>31,13; 42,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,24; 35,44</t>
+          <t>24,54; 35,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,42; 35,88</t>
+          <t>25,31; 35,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,84; 39,25</t>
+          <t>26,72; 40,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,01; 40,44</t>
+          <t>30,04; 40,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,94; 41,75</t>
+          <t>30,33; 41,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,01; 31,62</t>
+          <t>22,66; 32,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,15; 64,02</t>
+          <t>27,81; 36,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,75; 39,7</t>
+          <t>31,75; 39,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,45; 37,24</t>
+          <t>29,09; 36,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,27; 32,74</t>
+          <t>25,26; 32,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,99; 52,73</t>
+          <t>28,77; 36,57</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,39; 47,34</t>
+          <t>32,51; 47,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32,38; 46,6</t>
+          <t>32,49; 46,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55,48; 73,17</t>
+          <t>55,64; 72,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,72; 92,46</t>
+          <t>82,84; 90,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,63; 50,54</t>
+          <t>35,07; 50,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,16; 53,89</t>
+          <t>38,63; 53,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,11; 74,9</t>
+          <t>60,0; 75,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>86,94; 92,75</t>
+          <t>87,34; 92,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36,39; 47,18</t>
+          <t>36,01; 46,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37,38; 47,76</t>
+          <t>37,93; 48,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60,55; 71,55</t>
+          <t>60,3; 71,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,72; 91,85</t>
+          <t>86,45; 91,05</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,36; 30,83</t>
+          <t>18,84; 32,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24,82; 36,43</t>
+          <t>24,97; 36,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,02; 46,06</t>
+          <t>32,85; 46,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36,69; 48,44</t>
+          <t>36,09; 47,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,23; 38,29</t>
+          <t>25,54; 38,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,06; 45,56</t>
+          <t>33,08; 44,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,91; 51,68</t>
+          <t>38,69; 51,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46,64; 56,76</t>
+          <t>46,72; 56,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,96; 32,97</t>
+          <t>23,95; 32,71</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,51; 39,02</t>
+          <t>30,85; 38,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37,88; 47,04</t>
+          <t>37,96; 47,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42,89; 50,93</t>
+          <t>42,6; 50,64</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>57,62%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,02; 26,05</t>
+          <t>18,52; 26,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,55; 34,39</t>
+          <t>26,56; 35,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44,36; 54,56</t>
+          <t>45,16; 54,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54,99; 63,75</t>
+          <t>54,53; 63,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,22; 29,98</t>
+          <t>22,25; 29,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,74; 43,59</t>
+          <t>35,45; 43,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,38; 53,8</t>
+          <t>44,51; 53,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>19,83; 58,63</t>
+          <t>52,56; 59,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,4; 26,98</t>
+          <t>21,34; 26,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32,51; 38,1</t>
+          <t>32,14; 38,03</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45,91; 52,89</t>
+          <t>46,32; 52,95</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,35; 59,32</t>
+          <t>54,9; 60,4</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>71,19%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,98; 39,11</t>
+          <t>31,35; 39,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,78; 30,94</t>
+          <t>23,65; 30,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,11; 55,31</t>
+          <t>47,68; 55,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,32; 69,44</t>
+          <t>64,61; 71,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,3; 37,36</t>
+          <t>29,83; 38,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,22; 35,24</t>
+          <t>27,91; 35,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,49; 57,2</t>
+          <t>48,89; 56,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>70,87; 76,82</t>
+          <t>71,44; 76,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,66; 37,24</t>
+          <t>31,56; 37,24</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27,29; 32,36</t>
+          <t>27,33; 32,32</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49,51; 54,99</t>
+          <t>49,56; 55,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,6; 71,78</t>
+          <t>69,26; 73,41</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27,99; 31,63</t>
+          <t>27,98; 31,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27,78; 31,34</t>
+          <t>27,62; 31,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38,77; 42,68</t>
+          <t>38,88; 42,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41,74; 58,17</t>
+          <t>55,08; 58,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,71; 33,11</t>
+          <t>29,66; 33,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,55; 35,98</t>
+          <t>32,42; 36,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,61; 45,43</t>
+          <t>41,39; 45,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>44,37; 60,01</t>
+          <t>57,68; 60,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29,36; 31,92</t>
+          <t>29,28; 31,96</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30,74; 33,29</t>
+          <t>30,77; 33,3</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40,83; 43,41</t>
+          <t>40,78; 43,59</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>48,01; 57,99</t>
+          <t>56,82; 59,28</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288007</t>
+          <t>276962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>273202</t>
+          <t>293927</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>561209</t>
+          <t>570888</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42296; 66136</t>
+          <t>41930; 66980</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35170; 58809</t>
+          <t>36270; 59670</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45488; 74280</t>
+          <t>46895; 75980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>278707; 294157</t>
+          <t>266531; 284294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>60069; 87934</t>
+          <t>59482; 87068</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32245; 57597</t>
+          <t>32698; 56927</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63487; 93399</t>
+          <t>62980; 92147</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>267090; 277731</t>
+          <t>287485; 299002</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>107009; 145568</t>
+          <t>108169; 145596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>73508; 110202</t>
+          <t>74351; 111695</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>119003; 159417</t>
+          <t>117747; 160445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>550679; 569640</t>
+          <t>559643; 581183</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203817</t>
+          <t>210788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>209826</t>
+          <t>225345</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>413643</t>
+          <t>436133</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101624; 142154</t>
+          <t>103449; 142093</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>98348; 138740</t>
+          <t>102298; 140225</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81879; 116888</t>
+          <t>82385; 116670</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>176671; 231550</t>
+          <t>186097; 240690</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>111261; 149439</t>
+          <t>110392; 150258</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>107739; 148385</t>
+          <t>109306; 147642</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>117754; 153776</t>
+          <t>116707; 155329</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>190762; 229127</t>
+          <t>205092; 246851</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>225379; 280499</t>
+          <t>227043; 279423</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>219018; 276166</t>
+          <t>219298; 274552</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>208262; 260528</t>
+          <t>207668; 258709</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>379633; 447956</t>
+          <t>399313; 469267</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126278</t>
+          <t>124013</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>140676</t>
+          <t>142626</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>266954</t>
+          <t>266639</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43862; 70074</t>
+          <t>43374; 69335</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82267; 114987</t>
+          <t>84680; 116626</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91517; 125703</t>
+          <t>95012; 126831</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>109675; 144135</t>
+          <t>107949; 140476</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>57490; 86888</t>
+          <t>60506; 88628</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>101012; 136480</t>
+          <t>102270; 138580</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>104974; 138623</t>
+          <t>105047; 138228</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>124592; 155986</t>
+          <t>127241; 158310</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>109988; 149800</t>
+          <t>109083; 150115</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>194183; 243076</t>
+          <t>192337; 241866</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>206982; 254409</t>
+          <t>204496; 251804</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>243906; 289965</t>
+          <t>243764; 291289</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101828</t>
+          <t>121164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>188711</t>
+          <t>135470</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>290539</t>
+          <t>256635</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84025; 114298</t>
+          <t>83271; 114689</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75898; 110944</t>
+          <t>76826; 112519</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83895; 118409</t>
+          <t>83528; 117590</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80120; 121726</t>
+          <t>99077; 149064</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>89899; 121124</t>
+          <t>89977; 122066</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>106070; 143120</t>
+          <t>103987; 141763</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76785; 110295</t>
+          <t>79038; 112800</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>128536; 303113</t>
+          <t>116707; 154183</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180023; 225134</t>
+          <t>180016; 226404</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>193173; 244221</t>
+          <t>190822; 241033</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>171559; 222256</t>
+          <t>171505; 220806</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>227198; 413150</t>
+          <t>227398; 289047</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150421</t>
+          <t>165062</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>182811</t>
+          <t>198505</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>333232</t>
+          <t>363567</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55159; 80614</t>
+          <t>55351; 80651</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>62194; 89491</t>
+          <t>62397; 90040</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66141; 87230</t>
+          <t>66333; 86971</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144377; 155729</t>
+          <t>156806; 171879</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>61966; 87886</t>
+          <t>60991; 87021</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76191; 104854</t>
+          <t>75161; 103610</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87458; 108976</t>
+          <t>87298; 109408</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>175873; 187627</t>
+          <t>191972; 203591</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>125243; 162369</t>
+          <t>123933; 161432</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>144520; 184673</t>
+          <t>146667; 185847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160292; 189410</t>
+          <t>159635; 189847</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>325182; 340521</t>
+          <t>353661; 372491</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107964</t>
+          <t>104288</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>126977</t>
+          <t>129515</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>234941</t>
+          <t>233802</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34751; 58350</t>
+          <t>35660; 61984</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62054; 91072</t>
+          <t>62416; 92376</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77146; 107594</t>
+          <t>76735; 108339</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93106; 122900</t>
+          <t>90118; 118225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>51597; 78292</t>
+          <t>52234; 79161</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>90193; 120666</t>
+          <t>87601; 118753</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>96153; 127726</t>
+          <t>95615; 127603</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>114897; 139839</t>
+          <t>117532; 141928</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>94325; 129831</t>
+          <t>94297; 128787</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>157082; 200900</t>
+          <t>158792; 199663</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>182122; 226136</t>
+          <t>182499; 227039</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>214474; 254698</t>
+          <t>213529; 253870</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>358151</t>
+          <t>411121</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>356420</t>
+          <t>418648</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>714572</t>
+          <t>829770</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>83657; 120976</t>
+          <t>85991; 120707</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>152661; 197784</t>
+          <t>152740; 202109</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>196207; 241334</t>
+          <t>199724; 240668</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>330173; 382762</t>
+          <t>380946; 440458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>119821; 161677</t>
+          <t>119998; 160324</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>223740; 272845</t>
+          <t>221911; 272713</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>216147; 262027</t>
+          <t>216769; 261680</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>164268; 485631</t>
+          <t>389703; 442119</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>214821; 270757</t>
+          <t>214146; 270364</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>390473; 457595</t>
+          <t>386030; 456825</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>426626; 491546</t>
+          <t>430491; 492097</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>447863; 847552</t>
+          <t>790508; 869712</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>454744</t>
+          <t>525933</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>519216</t>
+          <t>599759</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>973959</t>
+          <t>1125692</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>163257; 206130</t>
+          <t>165245; 206415</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>150738; 196151</t>
+          <t>149935; 194681</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>301620; 354148</t>
+          <t>305259; 356042</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>211923; 630934</t>
+          <t>498138; 549823</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>173330; 220979</t>
+          <t>176431; 225308</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>198211; 247460</t>
+          <t>196039; 246672</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>342165; 395464</t>
+          <t>337963; 392738</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>498874; 540764</t>
+          <t>578903; 622594</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>354139; 416589</t>
+          <t>353052; 416514</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>364669; 432449</t>
+          <t>365204; 431831</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>659270; 732212</t>
+          <t>659907; 733328</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>606284; 1157496</t>
+          <t>1095245; 1160934</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1791211</t>
+          <t>1939330</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1997841</t>
+          <t>2143796</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3789051</t>
+          <t>4083126</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>687407; 777003</t>
+          <t>687219; 780082</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>809706; 913371</t>
+          <t>805087; 907853</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1032978; 1137089</t>
+          <t>1035993; 1135352</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1400399; 1951534</t>
+          <t>1872035; 2002868</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>813931; 907265</t>
+          <t>812786; 908419</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1023692; 1131777</t>
+          <t>1019742; 1132844</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1193046; 1302499</t>
+          <t>1186673; 1299243</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1587861; 2147506</t>
+          <t>2091003; 2197801</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1525596; 1658507</t>
+          <t>1521653; 1660640</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1863103; 2017148</t>
+          <t>1864483; 2018008</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2258370; 2401253</t>
+          <t>2255915; 2411091</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3328718; 4020537</t>
+          <t>3990974; 4163549</t>
         </is>
       </c>
     </row>
